--- a/data/industry/CFM/Channel SSD.xlsx
+++ b/data/industry/CFM/Channel SSD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D19BBC-9FB3-451B-975D-D7686321437A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8309EB02-9858-4C5D-88EB-41B49B267FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Channel SSD 120GB SATA" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -462,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -1233,6 +1236,98 @@
         <v>26</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>25</v>
+      </c>
+      <c r="F34" s="12">
+        <v>26.7</v>
+      </c>
+      <c r="G34" s="12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>25</v>
+      </c>
+      <c r="F35" s="12">
+        <v>26.7</v>
+      </c>
+      <c r="G35" s="12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>22</v>
+      </c>
+      <c r="F36" s="12">
+        <v>23.7</v>
+      </c>
+      <c r="G36" s="12">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>22</v>
+      </c>
+      <c r="F37" s="12">
+        <v>23.7</v>
+      </c>
+      <c r="G37" s="12">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1241,7 +1336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82D123-E18C-4733-B397-9C03328A1E65}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -2012,6 +2107,98 @@
         <v>52</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>50</v>
+      </c>
+      <c r="F34" s="14">
+        <v>53</v>
+      </c>
+      <c r="G34" s="14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>50</v>
+      </c>
+      <c r="F35" s="14">
+        <v>53</v>
+      </c>
+      <c r="G35" s="14">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>47</v>
+      </c>
+      <c r="F36" s="14">
+        <v>50</v>
+      </c>
+      <c r="G36" s="14">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>47</v>
+      </c>
+      <c r="F37" s="14">
+        <v>50</v>
+      </c>
+      <c r="G37" s="14">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2020,7 +2207,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DEEDA6-23E7-43DF-BF44-327B2DB18A4F}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -2791,6 +2978,98 @@
         <v>90</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>87.5</v>
+      </c>
+      <c r="F34" s="12">
+        <v>91</v>
+      </c>
+      <c r="G34" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>87.5</v>
+      </c>
+      <c r="F35" s="12">
+        <v>91</v>
+      </c>
+      <c r="G35" s="12">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>83.5</v>
+      </c>
+      <c r="F36" s="12">
+        <v>87</v>
+      </c>
+      <c r="G36" s="12">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>83.5</v>
+      </c>
+      <c r="F37" s="12">
+        <v>87</v>
+      </c>
+      <c r="G37" s="12">
+        <v>86</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2799,7 +3078,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F96F38-689A-4B46-8DFA-A4944FA7A43B}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -3570,6 +3849,98 @@
         <v>55</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="9">
+        <v>54</v>
+      </c>
+      <c r="F34" s="9">
+        <v>56</v>
+      </c>
+      <c r="G34" s="9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>54</v>
+      </c>
+      <c r="F35" s="9">
+        <v>56</v>
+      </c>
+      <c r="G35" s="9">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="9">
+        <v>51</v>
+      </c>
+      <c r="F36" s="9">
+        <v>53</v>
+      </c>
+      <c r="G36" s="9">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="9">
+        <v>51</v>
+      </c>
+      <c r="F37" s="9">
+        <v>53</v>
+      </c>
+      <c r="G37" s="9">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3578,7 +3949,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF9F8A-7AB5-472F-A579-46036402780F}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -4349,6 +4720,98 @@
         <v>105</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>104</v>
+      </c>
+      <c r="F34" s="12">
+        <v>106.2</v>
+      </c>
+      <c r="G34" s="12">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>104</v>
+      </c>
+      <c r="F35" s="12">
+        <v>106.2</v>
+      </c>
+      <c r="G35" s="12">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>99</v>
+      </c>
+      <c r="F36" s="12">
+        <v>101.2</v>
+      </c>
+      <c r="G36" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>99</v>
+      </c>
+      <c r="F37" s="12">
+        <v>101.2</v>
+      </c>
+      <c r="G37" s="12">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4357,7 +4820,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F1A6FD-F375-4FB8-8C30-C4A005067594}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -5128,6 +5591,98 @@
         <v>160</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="14">
+        <v>159</v>
+      </c>
+      <c r="F34" s="14">
+        <v>161</v>
+      </c>
+      <c r="G34" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="14">
+        <v>159</v>
+      </c>
+      <c r="F35" s="14">
+        <v>161</v>
+      </c>
+      <c r="G35" s="14">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="14">
+        <v>154</v>
+      </c>
+      <c r="F36" s="14">
+        <v>156</v>
+      </c>
+      <c r="G36" s="14">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="14">
+        <v>154</v>
+      </c>
+      <c r="F37" s="14">
+        <v>156</v>
+      </c>
+      <c r="G37" s="14">
+        <v>155</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5136,7 +5691,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720D88E-37F2-4EF2-B2CA-01688ACF7295}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -5907,6 +6462,98 @@
         <v>100</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>99</v>
+      </c>
+      <c r="F34" s="12">
+        <v>101</v>
+      </c>
+      <c r="G34" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>99</v>
+      </c>
+      <c r="F35" s="12">
+        <v>101</v>
+      </c>
+      <c r="G35" s="12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>97</v>
+      </c>
+      <c r="F36" s="12">
+        <v>99</v>
+      </c>
+      <c r="G36" s="12">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>97</v>
+      </c>
+      <c r="F37" s="12">
+        <v>99</v>
+      </c>
+      <c r="G37" s="12">
+        <v>98</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5915,7 +6562,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5A656-5B30-45CF-B579-A97C69E643A5}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -6686,6 +7333,98 @@
         <v>170</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>169</v>
+      </c>
+      <c r="F34" s="12">
+        <v>171</v>
+      </c>
+      <c r="G34" s="12">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>169</v>
+      </c>
+      <c r="F35" s="12">
+        <v>171</v>
+      </c>
+      <c r="G35" s="12">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>164</v>
+      </c>
+      <c r="F36" s="12">
+        <v>166</v>
+      </c>
+      <c r="G36" s="12">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>164</v>
+      </c>
+      <c r="F37" s="12">
+        <v>166</v>
+      </c>
+      <c r="G37" s="12">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6694,7 +7433,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3EDF89-A497-4D9B-AE60-D1EDE4F7FB0B}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
@@ -7465,6 +8204,98 @@
         <v>300</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="10">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="12">
+        <v>297</v>
+      </c>
+      <c r="F34" s="12">
+        <v>304</v>
+      </c>
+      <c r="G34" s="12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="10">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="12">
+        <v>297</v>
+      </c>
+      <c r="F35" s="12">
+        <v>304</v>
+      </c>
+      <c r="G35" s="12">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="B36" s="10">
+        <v>46112</v>
+      </c>
+      <c r="C36" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="12">
+        <v>292</v>
+      </c>
+      <c r="F36" s="12">
+        <v>299</v>
+      </c>
+      <c r="G36" s="12">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="B37" s="10">
+        <v>46119</v>
+      </c>
+      <c r="C37" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="12">
+        <v>292</v>
+      </c>
+      <c r="F37" s="12">
+        <v>299</v>
+      </c>
+      <c r="G37" s="12">
+        <v>295</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/Channel SSD.xlsx
+++ b/data/industry/CFM/Channel SSD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\CFM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8309EB02-9858-4C5D-88EB-41B49B267FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62B078B7-00DE-44C8-9263-F666EAD144A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="5" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Channel SSD 120GB SATA" sheetId="1" r:id="rId1"/>
@@ -28,15 +28,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -465,15 +462,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -1326,6 +1323,52 @@
       </c>
       <c r="G37" s="12">
         <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>21</v>
+      </c>
+      <c r="F38" s="12">
+        <v>22.7</v>
+      </c>
+      <c r="G38" s="12">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>20</v>
+      </c>
+      <c r="F39" s="12">
+        <v>21.7</v>
+      </c>
+      <c r="G39" s="12">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1336,15 +1379,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A82D123-E18C-4733-B397-9C03328A1E65}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -2197,6 +2240,52 @@
       </c>
       <c r="G37" s="14">
         <v>49</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>46</v>
+      </c>
+      <c r="F38" s="14">
+        <v>49</v>
+      </c>
+      <c r="G38" s="14">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>44</v>
+      </c>
+      <c r="F39" s="14">
+        <v>47</v>
+      </c>
+      <c r="G39" s="14">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2207,15 +2296,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11DEEDA6-23E7-43DF-BF44-327B2DB18A4F}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -3068,6 +3157,52 @@
       </c>
       <c r="G37" s="12">
         <v>86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>80.5</v>
+      </c>
+      <c r="F38" s="12">
+        <v>84</v>
+      </c>
+      <c r="G38" s="12">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>79.5</v>
+      </c>
+      <c r="F39" s="12">
+        <v>83</v>
+      </c>
+      <c r="G39" s="12">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -3078,15 +3213,15 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36F96F38-689A-4B46-8DFA-A4944FA7A43B}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="9"/>
-    <col min="7" max="7" width="11.25" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="9" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -3939,6 +4074,52 @@
       </c>
       <c r="G37" s="9">
         <v>52</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="9">
+        <v>49</v>
+      </c>
+      <c r="F38" s="9">
+        <v>51</v>
+      </c>
+      <c r="G38" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="9">
+        <v>48</v>
+      </c>
+      <c r="F39" s="9">
+        <v>50</v>
+      </c>
+      <c r="G39" s="9">
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -3949,15 +4130,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAF9F8A-7AB5-472F-A579-46036402780F}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -4810,6 +4991,52 @@
       </c>
       <c r="G37" s="12">
         <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>94</v>
+      </c>
+      <c r="F38" s="12">
+        <v>96</v>
+      </c>
+      <c r="G38" s="12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>92</v>
+      </c>
+      <c r="F39" s="12">
+        <v>94</v>
+      </c>
+      <c r="G39" s="12">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -4820,15 +5047,15 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F1A6FD-F375-4FB8-8C30-C4A005067594}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -5681,6 +5908,52 @@
       </c>
       <c r="G37" s="14">
         <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="14">
+        <v>149</v>
+      </c>
+      <c r="F38" s="14">
+        <v>151</v>
+      </c>
+      <c r="G38" s="14">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="14">
+        <v>147</v>
+      </c>
+      <c r="F39" s="14">
+        <v>149</v>
+      </c>
+      <c r="G39" s="14">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -5691,15 +5964,15 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F720D88E-37F2-4EF2-B2CA-01688ACF7295}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -6552,6 +6825,52 @@
       </c>
       <c r="G37" s="12">
         <v>98</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>94</v>
+      </c>
+      <c r="F38" s="12">
+        <v>96</v>
+      </c>
+      <c r="G38" s="12">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>92</v>
+      </c>
+      <c r="F39" s="12">
+        <v>94</v>
+      </c>
+      <c r="G39" s="12">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -6562,15 +6881,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CD5A656-5B30-45CF-B579-A97C69E643A5}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -7423,6 +7742,52 @@
       </c>
       <c r="G37" s="12">
         <v>165</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>159</v>
+      </c>
+      <c r="F38" s="12">
+        <v>161</v>
+      </c>
+      <c r="G38" s="12">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>155</v>
+      </c>
+      <c r="F39" s="12">
+        <v>157</v>
+      </c>
+      <c r="G39" s="12">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -7433,15 +7798,15 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A3EDF89-A497-4D9B-AE60-D1EDE4F7FB0B}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.69921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.19921875" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="8" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="12"/>
-    <col min="7" max="7" width="11.25" style="12" customWidth="1"/>
+    <col min="7" max="7" width="11.19921875" style="12" customWidth="1"/>
     <col min="8" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -8296,6 +8661,52 @@
         <v>295</v>
       </c>
     </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="B38" s="10">
+        <v>46126</v>
+      </c>
+      <c r="C38" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="12">
+        <v>287</v>
+      </c>
+      <c r="F38" s="12">
+        <v>294</v>
+      </c>
+      <c r="G38" s="12">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="B39" s="10">
+        <v>46133</v>
+      </c>
+      <c r="C39" s="7">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="12">
+        <v>277</v>
+      </c>
+      <c r="F39" s="12">
+        <v>284</v>
+      </c>
+      <c r="G39" s="12">
+        <v>280</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
